--- a/Result/profitability/3287.xlsx
+++ b/Result/profitability/3287.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3487500000000001</v>
+        <v>0.9912500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>26.66</v>
+        <v>29.2775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4125</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>27.68875</v>
+        <v>31.56125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.79</v>
       </c>
       <c r="M4" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>28.66125</v>
+        <v>31.99125</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.21</v>
       </c>
       <c r="M5" t="n">
-        <v>0.445</v>
+        <v>1.08625</v>
       </c>
       <c r="N5" t="n">
-        <v>29.55625</v>
+        <v>32.14624999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0.56625</v>
+        <v>1.07625</v>
       </c>
       <c r="N6" t="n">
-        <v>30.3175</v>
+        <v>34.81625</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5175000000000001</v>
+        <v>0.9637500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>34.0625</v>
+        <v>37.22875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0.39875</v>
+        <v>0.8812500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>36.1675</v>
+        <v>38.35625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.09</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2837500000000001</v>
+        <v>0.28375</v>
       </c>
       <c r="N9" t="n">
         <v>36.53</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>218</v>
+      </c>
+      <c r="D75" t="n">
+        <v>107</v>
+      </c>
+      <c r="E75" t="n">
+        <v>111</v>
+      </c>
+      <c r="F75" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>50</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>23.14%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>180</v>
+      </c>
+      <c r="J75" t="n">
+        <v>231</v>
+      </c>
+      <c r="K75" t="n">
+        <v>214</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.62625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="X75" t="n">
+        <v>3.821782178217822</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>17.51</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5245656081485919</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-19.73076923076923</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6867749419953595</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
